--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N11_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N11_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>59.47518254135433</v>
+        <v>9.664717162970078</v>
       </c>
       <c r="D2" t="n">
-        <v>58.87960197189712</v>
+        <v>9.567935320433284</v>
       </c>
       <c r="E2" t="n">
-        <v>29.13627643190084</v>
+        <v>4.734644920183888</v>
       </c>
       <c r="F2" t="n">
-        <v>29.29558404574722</v>
+        <v>4.760532407433923</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>39.64079519835915</v>
+        <v>6.441629219733362</v>
       </c>
       <c r="D3" t="n">
-        <v>39.09844944922479</v>
+        <v>6.35349803549903</v>
       </c>
       <c r="E3" t="n">
-        <v>29.13627643190084</v>
+        <v>4.734644920183888</v>
       </c>
       <c r="F3" t="n">
-        <v>29.29558404574722</v>
+        <v>4.760532407433923</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>53.65986412526586</v>
+        <v>8.719727920355702</v>
       </c>
       <c r="D4" t="n">
-        <v>54.17651085100594</v>
+        <v>8.803683013288467</v>
       </c>
       <c r="E4" t="n">
-        <v>29.13627643190084</v>
+        <v>4.734644920183888</v>
       </c>
       <c r="F4" t="n">
-        <v>29.29558404574722</v>
+        <v>4.760532407433923</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>68.80020723860734</v>
+        <v>11.18003367627369</v>
       </c>
       <c r="D5" t="n">
-        <v>69.47448184902125</v>
+        <v>11.28960330046595</v>
       </c>
       <c r="E5" t="n">
-        <v>29.13627643190084</v>
+        <v>4.734644920183888</v>
       </c>
       <c r="F5" t="n">
-        <v>29.29558404574722</v>
+        <v>4.760532407433923</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>105.3648462399041</v>
+        <v>17.12178751398442</v>
       </c>
       <c r="D6" t="n">
-        <v>104.5804868002828</v>
+        <v>16.99432910504596</v>
       </c>
       <c r="E6" t="n">
-        <v>29.13627643190084</v>
+        <v>4.734644920183888</v>
       </c>
       <c r="F6" t="n">
-        <v>29.29558404574722</v>
+        <v>4.760532407433923</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>9.014620415344723</v>
+        <v>1.464875817493517</v>
       </c>
       <c r="D7" t="n">
-        <v>7.926498548794149</v>
+        <v>1.288056014179049</v>
       </c>
       <c r="E7" t="n">
-        <v>29.13627643190084</v>
+        <v>4.734644920183888</v>
       </c>
       <c r="F7" t="n">
-        <v>29.29558404574722</v>
+        <v>4.760532407433923</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
